--- a/Design Files/Baseboard-v3.0/BOM/JLCPCB-BOM-Baseboard-v3.0-Development.xlsx
+++ b/Design Files/Baseboard-v3.0/BOM/JLCPCB-BOM-Baseboard-v3.0-Development.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="485">
   <si>
     <t>Comment</t>
   </si>
@@ -1457,6 +1457,15 @@
   </si>
   <si>
     <t>C99009</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>C2890594</t>
   </si>
 </sst>
 </file>
@@ -1618,25 +1627,25 @@
     <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf quotePrefix="1" borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf quotePrefix="1" borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf quotePrefix="1" borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf quotePrefix="1" borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf quotePrefix="1" borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf quotePrefix="1" borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1859,7 +1868,7 @@
     <col customWidth="1" min="2" max="2" width="36.0"/>
     <col customWidth="1" min="3" max="3" width="19.29"/>
     <col customWidth="1" min="4" max="4" width="26.57"/>
-    <col customWidth="1" min="5" max="26" width="8.71"/>
+    <col customWidth="1" min="5" max="6" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1894,10 +1903,10 @@
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -1925,7 +1934,7 @@
       <c r="B5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -1950,10 +1959,10 @@
       <c r="A7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -1964,7 +1973,7 @@
       <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1978,10 +1987,10 @@
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -2009,7 +2018,7 @@
       <c r="B11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>38</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -2037,7 +2046,7 @@
       <c r="B13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -2065,7 +2074,7 @@
       <c r="B15" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="5" t="s">
@@ -2093,7 +2102,7 @@
       <c r="B17" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -2121,7 +2130,7 @@
       <c r="B19" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -2149,7 +2158,7 @@
       <c r="B21" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -2177,7 +2186,7 @@
       <c r="B23" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D23" s="5" t="s">
@@ -2205,7 +2214,7 @@
       <c r="B25" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="5" t="s">
@@ -2233,7 +2242,7 @@
       <c r="B27" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D27" s="5" t="s">
@@ -2247,7 +2256,7 @@
       <c r="B28" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>89</v>
       </c>
       <c r="D28" s="5" t="s">
@@ -2275,7 +2284,7 @@
       <c r="B30" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D30" s="5" t="s">
@@ -2303,7 +2312,7 @@
       <c r="B32" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -2331,7 +2340,7 @@
       <c r="B34" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D34" s="5" t="s">
@@ -2359,7 +2368,7 @@
       <c r="B36" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="5" t="s">
@@ -2370,7 +2379,7 @@
       <c r="A37" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="3" t="s">
         <v>112</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -2387,7 +2396,7 @@
       <c r="B38" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -2415,7 +2424,7 @@
       <c r="B40" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="6" t="s">
         <v>121</v>
       </c>
       <c r="D40" s="5" t="s">
@@ -2443,7 +2452,7 @@
       <c r="B42" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="6" t="s">
         <v>129</v>
       </c>
       <c r="D42" s="5" t="s">
@@ -2471,7 +2480,7 @@
       <c r="B44" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="6" t="s">
         <v>137</v>
       </c>
       <c r="D44" s="5" t="s">
@@ -2499,7 +2508,7 @@
       <c r="B46" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D46" s="5" t="s">
@@ -2527,7 +2536,7 @@
       <c r="B48" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="6" t="s">
         <v>152</v>
       </c>
       <c r="D48" s="5" t="s">
@@ -2555,7 +2564,7 @@
       <c r="B50" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="6" t="s">
         <v>160</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -2583,7 +2592,7 @@
       <c r="B52" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="6" t="s">
         <v>168</v>
       </c>
       <c r="D52" s="5" t="s">
@@ -2611,7 +2620,7 @@
       <c r="B54" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="6" t="s">
         <v>176</v>
       </c>
       <c r="D54" s="5" t="s">
@@ -2639,7 +2648,7 @@
       <c r="B56" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="6" t="s">
         <v>183</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -2667,7 +2676,7 @@
       <c r="B58" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="6" t="s">
         <v>189</v>
       </c>
       <c r="D58" s="5" t="s">
@@ -2695,7 +2704,7 @@
       <c r="B60" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="6" t="s">
         <v>195</v>
       </c>
       <c r="D60" s="5" t="s">
@@ -2723,7 +2732,7 @@
       <c r="B62" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="6" t="s">
         <v>201</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -2751,7 +2760,7 @@
       <c r="B64" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="6" t="s">
         <v>209</v>
       </c>
       <c r="D64" s="5"/>
@@ -2777,7 +2786,7 @@
       <c r="B66" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="6" t="s">
         <v>209</v>
       </c>
       <c r="D66" s="5"/>
@@ -2803,7 +2812,7 @@
       <c r="B68" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="6" t="s">
         <v>220</v>
       </c>
       <c r="D68" s="5"/>
@@ -2829,7 +2838,7 @@
       <c r="B70" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="6" t="s">
         <v>227</v>
       </c>
       <c r="D70" s="5" t="s">
@@ -2857,7 +2866,7 @@
       <c r="B72" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="6" t="s">
         <v>235</v>
       </c>
       <c r="D72" s="5" t="s">
@@ -2885,7 +2894,7 @@
       <c r="B74" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="6" t="s">
         <v>243</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -2913,7 +2922,7 @@
       <c r="B76" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="6" t="s">
         <v>243</v>
       </c>
       <c r="D76" s="5" t="s">
@@ -2941,7 +2950,7 @@
       <c r="B78" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="6" t="s">
         <v>144</v>
       </c>
       <c r="D78" s="5" t="s">
@@ -2969,7 +2978,7 @@
       <c r="B80" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C80" s="6" t="s">
         <v>262</v>
       </c>
       <c r="D80" s="5" t="s">
@@ -2997,7 +3006,7 @@
       <c r="B82" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D82" s="5" t="s">
@@ -3025,7 +3034,7 @@
       <c r="B84" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="C84" s="6" t="s">
         <v>276</v>
       </c>
       <c r="D84" s="5" t="s">
@@ -3053,7 +3062,7 @@
       <c r="B86" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="6" t="s">
         <v>276</v>
       </c>
       <c r="D86" s="5" t="s">
@@ -3081,7 +3090,7 @@
       <c r="B88" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C88" s="6" t="s">
         <v>276</v>
       </c>
       <c r="D88" s="5" t="s">
@@ -3109,7 +3118,7 @@
       <c r="B90" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="C90" s="6" t="s">
         <v>292</v>
       </c>
       <c r="D90" s="5" t="s">
@@ -3134,10 +3143,10 @@
       <c r="A92" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="C92" s="6" t="s">
         <v>292</v>
       </c>
       <c r="D92" s="5" t="s">
@@ -3165,7 +3174,7 @@
       <c r="B94" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="C94" s="7" t="s">
+      <c r="C94" s="6" t="s">
         <v>276</v>
       </c>
       <c r="D94" s="5" t="s">
@@ -3176,7 +3185,7 @@
       <c r="A95" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="7" t="s">
         <v>309</v>
       </c>
       <c r="C95" s="4" t="s">
@@ -3193,7 +3202,7 @@
       <c r="B96" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="C96" s="7" t="s">
+      <c r="C96" s="6" t="s">
         <v>312</v>
       </c>
       <c r="D96" s="5" t="s">
@@ -3221,7 +3230,7 @@
       <c r="B98" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="C98" s="6" t="s">
         <v>319</v>
       </c>
       <c r="D98" s="5" t="s">
@@ -3246,10 +3255,10 @@
       <c r="A100" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="B100" s="6" t="s">
+      <c r="B100" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="C100" s="7" t="s">
+      <c r="C100" s="6" t="s">
         <v>276</v>
       </c>
       <c r="D100" s="5" t="s">
@@ -3277,7 +3286,7 @@
       <c r="B102" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="C102" s="7" t="s">
+      <c r="C102" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D102" s="5" t="s">
@@ -3305,7 +3314,7 @@
       <c r="B104" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="C104" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D104" s="5" t="s">
@@ -3333,7 +3342,7 @@
       <c r="B106" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="C106" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D106" s="5" t="s">
@@ -3361,7 +3370,7 @@
       <c r="B108" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="C108" s="6" t="s">
         <v>350</v>
       </c>
       <c r="D108" s="5" t="s">
@@ -3383,16 +3392,16 @@
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="10" t="s">
+      <c r="A110" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="C110" s="12" t="s">
+      <c r="C110" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="D110" s="10" t="s">
+      <c r="D110" s="8" t="s">
         <v>310</v>
       </c>
     </row>
@@ -3403,7 +3412,7 @@
       <c r="B111" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="C111" s="6" t="s">
         <v>292</v>
       </c>
       <c r="D111" s="5" t="s">
@@ -3445,7 +3454,7 @@
       <c r="B114" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="C114" s="7" t="s">
+      <c r="C114" s="6" t="s">
         <v>292</v>
       </c>
       <c r="D114" s="5" t="s">
@@ -3473,7 +3482,7 @@
       <c r="B116" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="C116" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D116" s="5" t="s">
@@ -3501,7 +3510,7 @@
       <c r="B118" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="C118" s="7" t="s">
+      <c r="C118" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D118" s="5" t="s">
@@ -3515,7 +3524,7 @@
       <c r="B119" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="C119" s="7" t="s">
+      <c r="C119" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D119" s="5" t="s">
@@ -3526,7 +3535,7 @@
       <c r="A120" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="B120" s="8" t="s">
+      <c r="B120" s="3" t="s">
         <v>380</v>
       </c>
       <c r="C120" s="4" t="s">
@@ -3543,7 +3552,7 @@
       <c r="B121" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="C121" s="7" t="s">
+      <c r="C121" s="6" t="s">
         <v>292</v>
       </c>
       <c r="D121" s="5" t="s">
@@ -3551,44 +3560,44 @@
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="10" t="s">
+      <c r="A122" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="B122" s="10" t="s">
+      <c r="B122" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="C122" s="12" t="s">
+      <c r="C122" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="D122" s="10" t="s">
+      <c r="D122" s="8" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="10" t="s">
+      <c r="A123" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="B123" s="10" t="s">
+      <c r="B123" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="C123" s="12" t="s">
+      <c r="C123" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="D123" s="8" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="10" t="s">
+      <c r="A124" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="B124" s="10" t="s">
+      <c r="B124" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="C124" s="12" t="s">
+      <c r="C124" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="D124" s="10" t="s">
+      <c r="D124" s="8" t="s">
         <v>391</v>
       </c>
     </row>
@@ -3613,7 +3622,7 @@
       <c r="B126" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="C126" s="7" t="s">
+      <c r="C126" s="6" t="s">
         <v>396</v>
       </c>
       <c r="D126" s="5" t="s">
@@ -3641,7 +3650,7 @@
       <c r="B128" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="C128" s="7" t="s">
+      <c r="C128" s="6" t="s">
         <v>404</v>
       </c>
       <c r="D128" s="5" t="s">
@@ -3669,7 +3678,7 @@
       <c r="B130" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="C130" s="7" t="s">
+      <c r="C130" s="6" t="s">
         <v>412</v>
       </c>
       <c r="D130" s="5" t="s">
@@ -3697,7 +3706,7 @@
       <c r="B132" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="C132" s="7" t="s">
+      <c r="C132" s="6" t="s">
         <v>420</v>
       </c>
       <c r="D132" s="5" t="s">
@@ -3725,7 +3734,7 @@
       <c r="B134" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="C134" s="7" t="s">
+      <c r="C134" s="6" t="s">
         <v>428</v>
       </c>
       <c r="D134" s="5" t="s">
@@ -3753,7 +3762,7 @@
       <c r="B136" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="C136" s="7" t="s">
+      <c r="C136" s="6" t="s">
         <v>435</v>
       </c>
       <c r="D136" s="5" t="s">
@@ -3781,7 +3790,7 @@
       <c r="B138" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="C138" s="7" t="s">
+      <c r="C138" s="6" t="s">
         <v>442</v>
       </c>
       <c r="D138" s="5" t="s">
@@ -3809,7 +3818,7 @@
       <c r="B140" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="C140" s="7" t="s">
+      <c r="C140" s="6" t="s">
         <v>137</v>
       </c>
       <c r="D140" s="5" t="s">
@@ -3837,7 +3846,7 @@
       <c r="B142" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="C142" s="7" t="s">
+      <c r="C142" s="6" t="s">
         <v>456</v>
       </c>
       <c r="D142" s="5" t="s">
@@ -3859,16 +3868,16 @@
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="11" t="s">
+      <c r="A144" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="B144" s="10" t="s">
+      <c r="B144" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="C144" s="12" t="s">
+      <c r="C144" s="10" t="s">
         <v>464</v>
       </c>
-      <c r="D144" s="10" t="s">
+      <c r="D144" s="8" t="s">
         <v>465</v>
       </c>
     </row>
@@ -3879,7 +3888,7 @@
       <c r="B145" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="C145" s="7" t="s">
+      <c r="C145" s="6" t="s">
         <v>468</v>
       </c>
       <c r="D145" s="5" t="s">
@@ -3907,7 +3916,7 @@
       <c r="B147" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="C147" s="7" t="s">
+      <c r="C147" s="6" t="s">
         <v>476</v>
       </c>
       <c r="D147" s="5" t="s">
@@ -3929,7 +3938,18 @@
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="13"/>
+      <c r="A149" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="D149" s="11" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="13"/>
@@ -4528,1962 +4548,658 @@
     <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="13"/>
     </row>
-    <row r="349" ht="15.75" customHeight="1">
-      <c r="A349" s="13"/>
-    </row>
-    <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="13"/>
-    </row>
-    <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="13"/>
-    </row>
-    <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="13"/>
-    </row>
-    <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="13"/>
-    </row>
-    <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="13"/>
-    </row>
-    <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="13"/>
-    </row>
-    <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="13"/>
-    </row>
-    <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="13"/>
-    </row>
-    <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="13"/>
-    </row>
-    <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="13"/>
-    </row>
-    <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="13"/>
-    </row>
-    <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="13"/>
-    </row>
-    <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="13"/>
-    </row>
-    <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="13"/>
-    </row>
-    <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="13"/>
-    </row>
-    <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="13"/>
-    </row>
-    <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="13"/>
-    </row>
-    <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="13"/>
-    </row>
-    <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="13"/>
-    </row>
-    <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="13"/>
-    </row>
-    <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="13"/>
-    </row>
-    <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="13"/>
-    </row>
-    <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="13"/>
-    </row>
-    <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="13"/>
-    </row>
-    <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="13"/>
-    </row>
-    <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="13"/>
-    </row>
-    <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="13"/>
-    </row>
-    <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="13"/>
-    </row>
-    <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="13"/>
-    </row>
-    <row r="379" ht="15.75" customHeight="1">
-      <c r="A379" s="13"/>
-    </row>
-    <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="13"/>
-    </row>
-    <row r="381" ht="15.75" customHeight="1">
-      <c r="A381" s="13"/>
-    </row>
-    <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="13"/>
-    </row>
-    <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="13"/>
-    </row>
-    <row r="384" ht="15.75" customHeight="1">
-      <c r="A384" s="13"/>
-    </row>
-    <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="13"/>
-    </row>
-    <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="13"/>
-    </row>
-    <row r="387" ht="15.75" customHeight="1">
-      <c r="A387" s="13"/>
-    </row>
-    <row r="388" ht="15.75" customHeight="1">
-      <c r="A388" s="13"/>
-    </row>
-    <row r="389" ht="15.75" customHeight="1">
-      <c r="A389" s="13"/>
-    </row>
-    <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="13"/>
-    </row>
-    <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="13"/>
-    </row>
-    <row r="392" ht="15.75" customHeight="1">
-      <c r="A392" s="13"/>
-    </row>
-    <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="13"/>
-    </row>
-    <row r="394" ht="15.75" customHeight="1">
-      <c r="A394" s="13"/>
-    </row>
-    <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="13"/>
-    </row>
-    <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="13"/>
-    </row>
-    <row r="397" ht="15.75" customHeight="1">
-      <c r="A397" s="13"/>
-    </row>
-    <row r="398" ht="15.75" customHeight="1">
-      <c r="A398" s="13"/>
-    </row>
-    <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="13"/>
-    </row>
-    <row r="400" ht="15.75" customHeight="1">
-      <c r="A400" s="13"/>
-    </row>
-    <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="13"/>
-    </row>
-    <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="13"/>
-    </row>
-    <row r="403" ht="15.75" customHeight="1">
-      <c r="A403" s="13"/>
-    </row>
-    <row r="404" ht="15.75" customHeight="1">
-      <c r="A404" s="13"/>
-    </row>
-    <row r="405" ht="15.75" customHeight="1">
-      <c r="A405" s="13"/>
-    </row>
-    <row r="406" ht="15.75" customHeight="1">
-      <c r="A406" s="13"/>
-    </row>
-    <row r="407" ht="15.75" customHeight="1">
-      <c r="A407" s="13"/>
-    </row>
-    <row r="408" ht="15.75" customHeight="1">
-      <c r="A408" s="13"/>
-    </row>
-    <row r="409" ht="15.75" customHeight="1">
-      <c r="A409" s="13"/>
-    </row>
-    <row r="410" ht="15.75" customHeight="1">
-      <c r="A410" s="13"/>
-    </row>
-    <row r="411" ht="15.75" customHeight="1">
-      <c r="A411" s="13"/>
-    </row>
-    <row r="412" ht="15.75" customHeight="1">
-      <c r="A412" s="13"/>
-    </row>
-    <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="13"/>
-    </row>
-    <row r="414" ht="15.75" customHeight="1">
-      <c r="A414" s="13"/>
-    </row>
-    <row r="415" ht="15.75" customHeight="1">
-      <c r="A415" s="13"/>
-    </row>
-    <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="13"/>
-    </row>
-    <row r="417" ht="15.75" customHeight="1">
-      <c r="A417" s="13"/>
-    </row>
-    <row r="418" ht="15.75" customHeight="1">
-      <c r="A418" s="13"/>
-    </row>
-    <row r="419" ht="15.75" customHeight="1">
-      <c r="A419" s="13"/>
-    </row>
-    <row r="420" ht="15.75" customHeight="1">
-      <c r="A420" s="13"/>
-    </row>
-    <row r="421" ht="15.75" customHeight="1">
-      <c r="A421" s="13"/>
-    </row>
-    <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="13"/>
-    </row>
-    <row r="423" ht="15.75" customHeight="1">
-      <c r="A423" s="13"/>
-    </row>
-    <row r="424" ht="15.75" customHeight="1">
-      <c r="A424" s="13"/>
-    </row>
-    <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="13"/>
-    </row>
-    <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="13"/>
-    </row>
-    <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="13"/>
-    </row>
-    <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="13"/>
-    </row>
-    <row r="429" ht="15.75" customHeight="1">
-      <c r="A429" s="13"/>
-    </row>
-    <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="13"/>
-    </row>
-    <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="13"/>
-    </row>
-    <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="13"/>
-    </row>
-    <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="13"/>
-    </row>
-    <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="13"/>
-    </row>
-    <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="13"/>
-    </row>
-    <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="13"/>
-    </row>
-    <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="13"/>
-    </row>
-    <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="13"/>
-    </row>
-    <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="13"/>
-    </row>
-    <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="13"/>
-    </row>
-    <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="13"/>
-    </row>
-    <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="13"/>
-    </row>
-    <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="13"/>
-    </row>
-    <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="13"/>
-    </row>
-    <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="13"/>
-    </row>
-    <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="13"/>
-    </row>
-    <row r="447" ht="15.75" customHeight="1">
-      <c r="A447" s="13"/>
-    </row>
-    <row r="448" ht="15.75" customHeight="1">
-      <c r="A448" s="13"/>
-    </row>
-    <row r="449" ht="15.75" customHeight="1">
-      <c r="A449" s="13"/>
-    </row>
-    <row r="450" ht="15.75" customHeight="1">
-      <c r="A450" s="13"/>
-    </row>
-    <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="13"/>
-    </row>
-    <row r="452" ht="15.75" customHeight="1">
-      <c r="A452" s="13"/>
-    </row>
-    <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="13"/>
-    </row>
-    <row r="454" ht="15.75" customHeight="1">
-      <c r="A454" s="13"/>
-    </row>
-    <row r="455" ht="15.75" customHeight="1">
-      <c r="A455" s="13"/>
-    </row>
-    <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="13"/>
-    </row>
-    <row r="457" ht="15.75" customHeight="1">
-      <c r="A457" s="13"/>
-    </row>
-    <row r="458" ht="15.75" customHeight="1">
-      <c r="A458" s="13"/>
-    </row>
-    <row r="459" ht="15.75" customHeight="1">
-      <c r="A459" s="13"/>
-    </row>
-    <row r="460" ht="15.75" customHeight="1">
-      <c r="A460" s="13"/>
-    </row>
-    <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="13"/>
-    </row>
-    <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="13"/>
-    </row>
-    <row r="463" ht="15.75" customHeight="1">
-      <c r="A463" s="13"/>
-    </row>
-    <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="13"/>
-    </row>
-    <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="13"/>
-    </row>
-    <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="13"/>
-    </row>
-    <row r="467" ht="15.75" customHeight="1">
-      <c r="A467" s="13"/>
-    </row>
-    <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="13"/>
-    </row>
-    <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="13"/>
-    </row>
-    <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="13"/>
-    </row>
-    <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="13"/>
-    </row>
-    <row r="472" ht="15.75" customHeight="1">
-      <c r="A472" s="13"/>
-    </row>
-    <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="13"/>
-    </row>
-    <row r="474" ht="15.75" customHeight="1">
-      <c r="A474" s="13"/>
-    </row>
-    <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="13"/>
-    </row>
-    <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="13"/>
-    </row>
-    <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="13"/>
-    </row>
-    <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="13"/>
-    </row>
-    <row r="479" ht="15.75" customHeight="1">
-      <c r="A479" s="13"/>
-    </row>
-    <row r="480" ht="15.75" customHeight="1">
-      <c r="A480" s="13"/>
-    </row>
-    <row r="481" ht="15.75" customHeight="1">
-      <c r="A481" s="13"/>
-    </row>
-    <row r="482" ht="15.75" customHeight="1">
-      <c r="A482" s="13"/>
-    </row>
-    <row r="483" ht="15.75" customHeight="1">
-      <c r="A483" s="13"/>
-    </row>
-    <row r="484" ht="15.75" customHeight="1">
-      <c r="A484" s="13"/>
-    </row>
-    <row r="485" ht="15.75" customHeight="1">
-      <c r="A485" s="13"/>
-    </row>
-    <row r="486" ht="15.75" customHeight="1">
-      <c r="A486" s="13"/>
-    </row>
-    <row r="487" ht="15.75" customHeight="1">
-      <c r="A487" s="13"/>
-    </row>
-    <row r="488" ht="15.75" customHeight="1">
-      <c r="A488" s="13"/>
-    </row>
-    <row r="489" ht="15.75" customHeight="1">
-      <c r="A489" s="13"/>
-    </row>
-    <row r="490" ht="15.75" customHeight="1">
-      <c r="A490" s="13"/>
-    </row>
-    <row r="491" ht="15.75" customHeight="1">
-      <c r="A491" s="13"/>
-    </row>
-    <row r="492" ht="15.75" customHeight="1">
-      <c r="A492" s="13"/>
-    </row>
-    <row r="493" ht="15.75" customHeight="1">
-      <c r="A493" s="13"/>
-    </row>
-    <row r="494" ht="15.75" customHeight="1">
-      <c r="A494" s="13"/>
-    </row>
-    <row r="495" ht="15.75" customHeight="1">
-      <c r="A495" s="13"/>
-    </row>
-    <row r="496" ht="15.75" customHeight="1">
-      <c r="A496" s="13"/>
-    </row>
-    <row r="497" ht="15.75" customHeight="1">
-      <c r="A497" s="13"/>
-    </row>
-    <row r="498" ht="15.75" customHeight="1">
-      <c r="A498" s="13"/>
-    </row>
-    <row r="499" ht="15.75" customHeight="1">
-      <c r="A499" s="13"/>
-    </row>
-    <row r="500" ht="15.75" customHeight="1">
-      <c r="A500" s="13"/>
-    </row>
-    <row r="501" ht="15.75" customHeight="1">
-      <c r="A501" s="13"/>
-    </row>
-    <row r="502" ht="15.75" customHeight="1">
-      <c r="A502" s="13"/>
-    </row>
-    <row r="503" ht="15.75" customHeight="1">
-      <c r="A503" s="13"/>
-    </row>
-    <row r="504" ht="15.75" customHeight="1">
-      <c r="A504" s="13"/>
-    </row>
-    <row r="505" ht="15.75" customHeight="1">
-      <c r="A505" s="13"/>
-    </row>
-    <row r="506" ht="15.75" customHeight="1">
-      <c r="A506" s="13"/>
-    </row>
-    <row r="507" ht="15.75" customHeight="1">
-      <c r="A507" s="13"/>
-    </row>
-    <row r="508" ht="15.75" customHeight="1">
-      <c r="A508" s="13"/>
-    </row>
-    <row r="509" ht="15.75" customHeight="1">
-      <c r="A509" s="13"/>
-    </row>
-    <row r="510" ht="15.75" customHeight="1">
-      <c r="A510" s="13"/>
-    </row>
-    <row r="511" ht="15.75" customHeight="1">
-      <c r="A511" s="13"/>
-    </row>
-    <row r="512" ht="15.75" customHeight="1">
-      <c r="A512" s="13"/>
-    </row>
-    <row r="513" ht="15.75" customHeight="1">
-      <c r="A513" s="13"/>
-    </row>
-    <row r="514" ht="15.75" customHeight="1">
-      <c r="A514" s="13"/>
-    </row>
-    <row r="515" ht="15.75" customHeight="1">
-      <c r="A515" s="13"/>
-    </row>
-    <row r="516" ht="15.75" customHeight="1">
-      <c r="A516" s="13"/>
-    </row>
-    <row r="517" ht="15.75" customHeight="1">
-      <c r="A517" s="13"/>
-    </row>
-    <row r="518" ht="15.75" customHeight="1">
-      <c r="A518" s="13"/>
-    </row>
-    <row r="519" ht="15.75" customHeight="1">
-      <c r="A519" s="13"/>
-    </row>
-    <row r="520" ht="15.75" customHeight="1">
-      <c r="A520" s="13"/>
-    </row>
-    <row r="521" ht="15.75" customHeight="1">
-      <c r="A521" s="13"/>
-    </row>
-    <row r="522" ht="15.75" customHeight="1">
-      <c r="A522" s="13"/>
-    </row>
-    <row r="523" ht="15.75" customHeight="1">
-      <c r="A523" s="13"/>
-    </row>
-    <row r="524" ht="15.75" customHeight="1">
-      <c r="A524" s="13"/>
-    </row>
-    <row r="525" ht="15.75" customHeight="1">
-      <c r="A525" s="13"/>
-    </row>
-    <row r="526" ht="15.75" customHeight="1">
-      <c r="A526" s="13"/>
-    </row>
-    <row r="527" ht="15.75" customHeight="1">
-      <c r="A527" s="13"/>
-    </row>
-    <row r="528" ht="15.75" customHeight="1">
-      <c r="A528" s="13"/>
-    </row>
-    <row r="529" ht="15.75" customHeight="1">
-      <c r="A529" s="13"/>
-    </row>
-    <row r="530" ht="15.75" customHeight="1">
-      <c r="A530" s="13"/>
-    </row>
-    <row r="531" ht="15.75" customHeight="1">
-      <c r="A531" s="13"/>
-    </row>
-    <row r="532" ht="15.75" customHeight="1">
-      <c r="A532" s="13"/>
-    </row>
-    <row r="533" ht="15.75" customHeight="1">
-      <c r="A533" s="13"/>
-    </row>
-    <row r="534" ht="15.75" customHeight="1">
-      <c r="A534" s="13"/>
-    </row>
-    <row r="535" ht="15.75" customHeight="1">
-      <c r="A535" s="13"/>
-    </row>
-    <row r="536" ht="15.75" customHeight="1">
-      <c r="A536" s="13"/>
-    </row>
-    <row r="537" ht="15.75" customHeight="1">
-      <c r="A537" s="13"/>
-    </row>
-    <row r="538" ht="15.75" customHeight="1">
-      <c r="A538" s="13"/>
-    </row>
-    <row r="539" ht="15.75" customHeight="1">
-      <c r="A539" s="13"/>
-    </row>
-    <row r="540" ht="15.75" customHeight="1">
-      <c r="A540" s="13"/>
-    </row>
-    <row r="541" ht="15.75" customHeight="1">
-      <c r="A541" s="13"/>
-    </row>
-    <row r="542" ht="15.75" customHeight="1">
-      <c r="A542" s="13"/>
-    </row>
-    <row r="543" ht="15.75" customHeight="1">
-      <c r="A543" s="13"/>
-    </row>
-    <row r="544" ht="15.75" customHeight="1">
-      <c r="A544" s="13"/>
-    </row>
-    <row r="545" ht="15.75" customHeight="1">
-      <c r="A545" s="13"/>
-    </row>
-    <row r="546" ht="15.75" customHeight="1">
-      <c r="A546" s="13"/>
-    </row>
-    <row r="547" ht="15.75" customHeight="1">
-      <c r="A547" s="13"/>
-    </row>
-    <row r="548" ht="15.75" customHeight="1">
-      <c r="A548" s="13"/>
-    </row>
-    <row r="549" ht="15.75" customHeight="1">
-      <c r="A549" s="13"/>
-    </row>
-    <row r="550" ht="15.75" customHeight="1">
-      <c r="A550" s="13"/>
-    </row>
-    <row r="551" ht="15.75" customHeight="1">
-      <c r="A551" s="13"/>
-    </row>
-    <row r="552" ht="15.75" customHeight="1">
-      <c r="A552" s="13"/>
-    </row>
-    <row r="553" ht="15.75" customHeight="1">
-      <c r="A553" s="13"/>
-    </row>
-    <row r="554" ht="15.75" customHeight="1">
-      <c r="A554" s="13"/>
-    </row>
-    <row r="555" ht="15.75" customHeight="1">
-      <c r="A555" s="13"/>
-    </row>
-    <row r="556" ht="15.75" customHeight="1">
-      <c r="A556" s="13"/>
-    </row>
-    <row r="557" ht="15.75" customHeight="1">
-      <c r="A557" s="13"/>
-    </row>
-    <row r="558" ht="15.75" customHeight="1">
-      <c r="A558" s="13"/>
-    </row>
-    <row r="559" ht="15.75" customHeight="1">
-      <c r="A559" s="13"/>
-    </row>
-    <row r="560" ht="15.75" customHeight="1">
-      <c r="A560" s="13"/>
-    </row>
-    <row r="561" ht="15.75" customHeight="1">
-      <c r="A561" s="13"/>
-    </row>
-    <row r="562" ht="15.75" customHeight="1">
-      <c r="A562" s="13"/>
-    </row>
-    <row r="563" ht="15.75" customHeight="1">
-      <c r="A563" s="13"/>
-    </row>
-    <row r="564" ht="15.75" customHeight="1">
-      <c r="A564" s="13"/>
-    </row>
-    <row r="565" ht="15.75" customHeight="1">
-      <c r="A565" s="13"/>
-    </row>
-    <row r="566" ht="15.75" customHeight="1">
-      <c r="A566" s="13"/>
-    </row>
-    <row r="567" ht="15.75" customHeight="1">
-      <c r="A567" s="13"/>
-    </row>
-    <row r="568" ht="15.75" customHeight="1">
-      <c r="A568" s="13"/>
-    </row>
-    <row r="569" ht="15.75" customHeight="1">
-      <c r="A569" s="13"/>
-    </row>
-    <row r="570" ht="15.75" customHeight="1">
-      <c r="A570" s="13"/>
-    </row>
-    <row r="571" ht="15.75" customHeight="1">
-      <c r="A571" s="13"/>
-    </row>
-    <row r="572" ht="15.75" customHeight="1">
-      <c r="A572" s="13"/>
-    </row>
-    <row r="573" ht="15.75" customHeight="1">
-      <c r="A573" s="13"/>
-    </row>
-    <row r="574" ht="15.75" customHeight="1">
-      <c r="A574" s="13"/>
-    </row>
-    <row r="575" ht="15.75" customHeight="1">
-      <c r="A575" s="13"/>
-    </row>
-    <row r="576" ht="15.75" customHeight="1">
-      <c r="A576" s="13"/>
-    </row>
-    <row r="577" ht="15.75" customHeight="1">
-      <c r="A577" s="13"/>
-    </row>
-    <row r="578" ht="15.75" customHeight="1">
-      <c r="A578" s="13"/>
-    </row>
-    <row r="579" ht="15.75" customHeight="1">
-      <c r="A579" s="13"/>
-    </row>
-    <row r="580" ht="15.75" customHeight="1">
-      <c r="A580" s="13"/>
-    </row>
-    <row r="581" ht="15.75" customHeight="1">
-      <c r="A581" s="13"/>
-    </row>
-    <row r="582" ht="15.75" customHeight="1">
-      <c r="A582" s="13"/>
-    </row>
-    <row r="583" ht="15.75" customHeight="1">
-      <c r="A583" s="13"/>
-    </row>
-    <row r="584" ht="15.75" customHeight="1">
-      <c r="A584" s="13"/>
-    </row>
-    <row r="585" ht="15.75" customHeight="1">
-      <c r="A585" s="13"/>
-    </row>
-    <row r="586" ht="15.75" customHeight="1">
-      <c r="A586" s="13"/>
-    </row>
-    <row r="587" ht="15.75" customHeight="1">
-      <c r="A587" s="13"/>
-    </row>
-    <row r="588" ht="15.75" customHeight="1">
-      <c r="A588" s="13"/>
-    </row>
-    <row r="589" ht="15.75" customHeight="1">
-      <c r="A589" s="13"/>
-    </row>
-    <row r="590" ht="15.75" customHeight="1">
-      <c r="A590" s="13"/>
-    </row>
-    <row r="591" ht="15.75" customHeight="1">
-      <c r="A591" s="13"/>
-    </row>
-    <row r="592" ht="15.75" customHeight="1">
-      <c r="A592" s="13"/>
-    </row>
-    <row r="593" ht="15.75" customHeight="1">
-      <c r="A593" s="13"/>
-    </row>
-    <row r="594" ht="15.75" customHeight="1">
-      <c r="A594" s="13"/>
-    </row>
-    <row r="595" ht="15.75" customHeight="1">
-      <c r="A595" s="13"/>
-    </row>
-    <row r="596" ht="15.75" customHeight="1">
-      <c r="A596" s="13"/>
-    </row>
-    <row r="597" ht="15.75" customHeight="1">
-      <c r="A597" s="13"/>
-    </row>
-    <row r="598" ht="15.75" customHeight="1">
-      <c r="A598" s="13"/>
-    </row>
-    <row r="599" ht="15.75" customHeight="1">
-      <c r="A599" s="13"/>
-    </row>
-    <row r="600" ht="15.75" customHeight="1">
-      <c r="A600" s="13"/>
-    </row>
-    <row r="601" ht="15.75" customHeight="1">
-      <c r="A601" s="13"/>
-    </row>
-    <row r="602" ht="15.75" customHeight="1">
-      <c r="A602" s="13"/>
-    </row>
-    <row r="603" ht="15.75" customHeight="1">
-      <c r="A603" s="13"/>
-    </row>
-    <row r="604" ht="15.75" customHeight="1">
-      <c r="A604" s="13"/>
-    </row>
-    <row r="605" ht="15.75" customHeight="1">
-      <c r="A605" s="13"/>
-    </row>
-    <row r="606" ht="15.75" customHeight="1">
-      <c r="A606" s="13"/>
-    </row>
-    <row r="607" ht="15.75" customHeight="1">
-      <c r="A607" s="13"/>
-    </row>
-    <row r="608" ht="15.75" customHeight="1">
-      <c r="A608" s="13"/>
-    </row>
-    <row r="609" ht="15.75" customHeight="1">
-      <c r="A609" s="13"/>
-    </row>
-    <row r="610" ht="15.75" customHeight="1">
-      <c r="A610" s="13"/>
-    </row>
-    <row r="611" ht="15.75" customHeight="1">
-      <c r="A611" s="13"/>
-    </row>
-    <row r="612" ht="15.75" customHeight="1">
-      <c r="A612" s="13"/>
-    </row>
-    <row r="613" ht="15.75" customHeight="1">
-      <c r="A613" s="13"/>
-    </row>
-    <row r="614" ht="15.75" customHeight="1">
-      <c r="A614" s="13"/>
-    </row>
-    <row r="615" ht="15.75" customHeight="1">
-      <c r="A615" s="13"/>
-    </row>
-    <row r="616" ht="15.75" customHeight="1">
-      <c r="A616" s="13"/>
-    </row>
-    <row r="617" ht="15.75" customHeight="1">
-      <c r="A617" s="13"/>
-    </row>
-    <row r="618" ht="15.75" customHeight="1">
-      <c r="A618" s="13"/>
-    </row>
-    <row r="619" ht="15.75" customHeight="1">
-      <c r="A619" s="13"/>
-    </row>
-    <row r="620" ht="15.75" customHeight="1">
-      <c r="A620" s="13"/>
-    </row>
-    <row r="621" ht="15.75" customHeight="1">
-      <c r="A621" s="13"/>
-    </row>
-    <row r="622" ht="15.75" customHeight="1">
-      <c r="A622" s="13"/>
-    </row>
-    <row r="623" ht="15.75" customHeight="1">
-      <c r="A623" s="13"/>
-    </row>
-    <row r="624" ht="15.75" customHeight="1">
-      <c r="A624" s="13"/>
-    </row>
-    <row r="625" ht="15.75" customHeight="1">
-      <c r="A625" s="13"/>
-    </row>
-    <row r="626" ht="15.75" customHeight="1">
-      <c r="A626" s="13"/>
-    </row>
-    <row r="627" ht="15.75" customHeight="1">
-      <c r="A627" s="13"/>
-    </row>
-    <row r="628" ht="15.75" customHeight="1">
-      <c r="A628" s="13"/>
-    </row>
-    <row r="629" ht="15.75" customHeight="1">
-      <c r="A629" s="13"/>
-    </row>
-    <row r="630" ht="15.75" customHeight="1">
-      <c r="A630" s="13"/>
-    </row>
-    <row r="631" ht="15.75" customHeight="1">
-      <c r="A631" s="13"/>
-    </row>
-    <row r="632" ht="15.75" customHeight="1">
-      <c r="A632" s="13"/>
-    </row>
-    <row r="633" ht="15.75" customHeight="1">
-      <c r="A633" s="13"/>
-    </row>
-    <row r="634" ht="15.75" customHeight="1">
-      <c r="A634" s="13"/>
-    </row>
-    <row r="635" ht="15.75" customHeight="1">
-      <c r="A635" s="13"/>
-    </row>
-    <row r="636" ht="15.75" customHeight="1">
-      <c r="A636" s="13"/>
-    </row>
-    <row r="637" ht="15.75" customHeight="1">
-      <c r="A637" s="13"/>
-    </row>
-    <row r="638" ht="15.75" customHeight="1">
-      <c r="A638" s="13"/>
-    </row>
-    <row r="639" ht="15.75" customHeight="1">
-      <c r="A639" s="13"/>
-    </row>
-    <row r="640" ht="15.75" customHeight="1">
-      <c r="A640" s="13"/>
-    </row>
-    <row r="641" ht="15.75" customHeight="1">
-      <c r="A641" s="13"/>
-    </row>
-    <row r="642" ht="15.75" customHeight="1">
-      <c r="A642" s="13"/>
-    </row>
-    <row r="643" ht="15.75" customHeight="1">
-      <c r="A643" s="13"/>
-    </row>
-    <row r="644" ht="15.75" customHeight="1">
-      <c r="A644" s="13"/>
-    </row>
-    <row r="645" ht="15.75" customHeight="1">
-      <c r="A645" s="13"/>
-    </row>
-    <row r="646" ht="15.75" customHeight="1">
-      <c r="A646" s="13"/>
-    </row>
-    <row r="647" ht="15.75" customHeight="1">
-      <c r="A647" s="13"/>
-    </row>
-    <row r="648" ht="15.75" customHeight="1">
-      <c r="A648" s="13"/>
-    </row>
-    <row r="649" ht="15.75" customHeight="1">
-      <c r="A649" s="13"/>
-    </row>
-    <row r="650" ht="15.75" customHeight="1">
-      <c r="A650" s="13"/>
-    </row>
-    <row r="651" ht="15.75" customHeight="1">
-      <c r="A651" s="13"/>
-    </row>
-    <row r="652" ht="15.75" customHeight="1">
-      <c r="A652" s="13"/>
-    </row>
-    <row r="653" ht="15.75" customHeight="1">
-      <c r="A653" s="13"/>
-    </row>
-    <row r="654" ht="15.75" customHeight="1">
-      <c r="A654" s="13"/>
-    </row>
-    <row r="655" ht="15.75" customHeight="1">
-      <c r="A655" s="13"/>
-    </row>
-    <row r="656" ht="15.75" customHeight="1">
-      <c r="A656" s="13"/>
-    </row>
-    <row r="657" ht="15.75" customHeight="1">
-      <c r="A657" s="13"/>
-    </row>
-    <row r="658" ht="15.75" customHeight="1">
-      <c r="A658" s="13"/>
-    </row>
-    <row r="659" ht="15.75" customHeight="1">
-      <c r="A659" s="13"/>
-    </row>
-    <row r="660" ht="15.75" customHeight="1">
-      <c r="A660" s="13"/>
-    </row>
-    <row r="661" ht="15.75" customHeight="1">
-      <c r="A661" s="13"/>
-    </row>
-    <row r="662" ht="15.75" customHeight="1">
-      <c r="A662" s="13"/>
-    </row>
-    <row r="663" ht="15.75" customHeight="1">
-      <c r="A663" s="13"/>
-    </row>
-    <row r="664" ht="15.75" customHeight="1">
-      <c r="A664" s="13"/>
-    </row>
-    <row r="665" ht="15.75" customHeight="1">
-      <c r="A665" s="13"/>
-    </row>
-    <row r="666" ht="15.75" customHeight="1">
-      <c r="A666" s="13"/>
-    </row>
-    <row r="667" ht="15.75" customHeight="1">
-      <c r="A667" s="13"/>
-    </row>
-    <row r="668" ht="15.75" customHeight="1">
-      <c r="A668" s="13"/>
-    </row>
-    <row r="669" ht="15.75" customHeight="1">
-      <c r="A669" s="13"/>
-    </row>
-    <row r="670" ht="15.75" customHeight="1">
-      <c r="A670" s="13"/>
-    </row>
-    <row r="671" ht="15.75" customHeight="1">
-      <c r="A671" s="13"/>
-    </row>
-    <row r="672" ht="15.75" customHeight="1">
-      <c r="A672" s="13"/>
-    </row>
-    <row r="673" ht="15.75" customHeight="1">
-      <c r="A673" s="13"/>
-    </row>
-    <row r="674" ht="15.75" customHeight="1">
-      <c r="A674" s="13"/>
-    </row>
-    <row r="675" ht="15.75" customHeight="1">
-      <c r="A675" s="13"/>
-    </row>
-    <row r="676" ht="15.75" customHeight="1">
-      <c r="A676" s="13"/>
-    </row>
-    <row r="677" ht="15.75" customHeight="1">
-      <c r="A677" s="13"/>
-    </row>
-    <row r="678" ht="15.75" customHeight="1">
-      <c r="A678" s="13"/>
-    </row>
-    <row r="679" ht="15.75" customHeight="1">
-      <c r="A679" s="13"/>
-    </row>
-    <row r="680" ht="15.75" customHeight="1">
-      <c r="A680" s="13"/>
-    </row>
-    <row r="681" ht="15.75" customHeight="1">
-      <c r="A681" s="13"/>
-    </row>
-    <row r="682" ht="15.75" customHeight="1">
-      <c r="A682" s="13"/>
-    </row>
-    <row r="683" ht="15.75" customHeight="1">
-      <c r="A683" s="13"/>
-    </row>
-    <row r="684" ht="15.75" customHeight="1">
-      <c r="A684" s="13"/>
-    </row>
-    <row r="685" ht="15.75" customHeight="1">
-      <c r="A685" s="13"/>
-    </row>
-    <row r="686" ht="15.75" customHeight="1">
-      <c r="A686" s="13"/>
-    </row>
-    <row r="687" ht="15.75" customHeight="1">
-      <c r="A687" s="13"/>
-    </row>
-    <row r="688" ht="15.75" customHeight="1">
-      <c r="A688" s="13"/>
-    </row>
-    <row r="689" ht="15.75" customHeight="1">
-      <c r="A689" s="13"/>
-    </row>
-    <row r="690" ht="15.75" customHeight="1">
-      <c r="A690" s="13"/>
-    </row>
-    <row r="691" ht="15.75" customHeight="1">
-      <c r="A691" s="13"/>
-    </row>
-    <row r="692" ht="15.75" customHeight="1">
-      <c r="A692" s="13"/>
-    </row>
-    <row r="693" ht="15.75" customHeight="1">
-      <c r="A693" s="13"/>
-    </row>
-    <row r="694" ht="15.75" customHeight="1">
-      <c r="A694" s="13"/>
-    </row>
-    <row r="695" ht="15.75" customHeight="1">
-      <c r="A695" s="13"/>
-    </row>
-    <row r="696" ht="15.75" customHeight="1">
-      <c r="A696" s="13"/>
-    </row>
-    <row r="697" ht="15.75" customHeight="1">
-      <c r="A697" s="13"/>
-    </row>
-    <row r="698" ht="15.75" customHeight="1">
-      <c r="A698" s="13"/>
-    </row>
-    <row r="699" ht="15.75" customHeight="1">
-      <c r="A699" s="13"/>
-    </row>
-    <row r="700" ht="15.75" customHeight="1">
-      <c r="A700" s="13"/>
-    </row>
-    <row r="701" ht="15.75" customHeight="1">
-      <c r="A701" s="13"/>
-    </row>
-    <row r="702" ht="15.75" customHeight="1">
-      <c r="A702" s="13"/>
-    </row>
-    <row r="703" ht="15.75" customHeight="1">
-      <c r="A703" s="13"/>
-    </row>
-    <row r="704" ht="15.75" customHeight="1">
-      <c r="A704" s="13"/>
-    </row>
-    <row r="705" ht="15.75" customHeight="1">
-      <c r="A705" s="13"/>
-    </row>
-    <row r="706" ht="15.75" customHeight="1">
-      <c r="A706" s="13"/>
-    </row>
-    <row r="707" ht="15.75" customHeight="1">
-      <c r="A707" s="13"/>
-    </row>
-    <row r="708" ht="15.75" customHeight="1">
-      <c r="A708" s="13"/>
-    </row>
-    <row r="709" ht="15.75" customHeight="1">
-      <c r="A709" s="13"/>
-    </row>
-    <row r="710" ht="15.75" customHeight="1">
-      <c r="A710" s="13"/>
-    </row>
-    <row r="711" ht="15.75" customHeight="1">
-      <c r="A711" s="13"/>
-    </row>
-    <row r="712" ht="15.75" customHeight="1">
-      <c r="A712" s="13"/>
-    </row>
-    <row r="713" ht="15.75" customHeight="1">
-      <c r="A713" s="13"/>
-    </row>
-    <row r="714" ht="15.75" customHeight="1">
-      <c r="A714" s="13"/>
-    </row>
-    <row r="715" ht="15.75" customHeight="1">
-      <c r="A715" s="13"/>
-    </row>
-    <row r="716" ht="15.75" customHeight="1">
-      <c r="A716" s="13"/>
-    </row>
-    <row r="717" ht="15.75" customHeight="1">
-      <c r="A717" s="13"/>
-    </row>
-    <row r="718" ht="15.75" customHeight="1">
-      <c r="A718" s="13"/>
-    </row>
-    <row r="719" ht="15.75" customHeight="1">
-      <c r="A719" s="13"/>
-    </row>
-    <row r="720" ht="15.75" customHeight="1">
-      <c r="A720" s="13"/>
-    </row>
-    <row r="721" ht="15.75" customHeight="1">
-      <c r="A721" s="13"/>
-    </row>
-    <row r="722" ht="15.75" customHeight="1">
-      <c r="A722" s="13"/>
-    </row>
-    <row r="723" ht="15.75" customHeight="1">
-      <c r="A723" s="13"/>
-    </row>
-    <row r="724" ht="15.75" customHeight="1">
-      <c r="A724" s="13"/>
-    </row>
-    <row r="725" ht="15.75" customHeight="1">
-      <c r="A725" s="13"/>
-    </row>
-    <row r="726" ht="15.75" customHeight="1">
-      <c r="A726" s="13"/>
-    </row>
-    <row r="727" ht="15.75" customHeight="1">
-      <c r="A727" s="13"/>
-    </row>
-    <row r="728" ht="15.75" customHeight="1">
-      <c r="A728" s="13"/>
-    </row>
-    <row r="729" ht="15.75" customHeight="1">
-      <c r="A729" s="13"/>
-    </row>
-    <row r="730" ht="15.75" customHeight="1">
-      <c r="A730" s="13"/>
-    </row>
-    <row r="731" ht="15.75" customHeight="1">
-      <c r="A731" s="13"/>
-    </row>
-    <row r="732" ht="15.75" customHeight="1">
-      <c r="A732" s="13"/>
-    </row>
-    <row r="733" ht="15.75" customHeight="1">
-      <c r="A733" s="13"/>
-    </row>
-    <row r="734" ht="15.75" customHeight="1">
-      <c r="A734" s="13"/>
-    </row>
-    <row r="735" ht="15.75" customHeight="1">
-      <c r="A735" s="13"/>
-    </row>
-    <row r="736" ht="15.75" customHeight="1">
-      <c r="A736" s="13"/>
-    </row>
-    <row r="737" ht="15.75" customHeight="1">
-      <c r="A737" s="13"/>
-    </row>
-    <row r="738" ht="15.75" customHeight="1">
-      <c r="A738" s="13"/>
-    </row>
-    <row r="739" ht="15.75" customHeight="1">
-      <c r="A739" s="13"/>
-    </row>
-    <row r="740" ht="15.75" customHeight="1">
-      <c r="A740" s="13"/>
-    </row>
-    <row r="741" ht="15.75" customHeight="1">
-      <c r="A741" s="13"/>
-    </row>
-    <row r="742" ht="15.75" customHeight="1">
-      <c r="A742" s="13"/>
-    </row>
-    <row r="743" ht="15.75" customHeight="1">
-      <c r="A743" s="13"/>
-    </row>
-    <row r="744" ht="15.75" customHeight="1">
-      <c r="A744" s="13"/>
-    </row>
-    <row r="745" ht="15.75" customHeight="1">
-      <c r="A745" s="13"/>
-    </row>
-    <row r="746" ht="15.75" customHeight="1">
-      <c r="A746" s="13"/>
-    </row>
-    <row r="747" ht="15.75" customHeight="1">
-      <c r="A747" s="13"/>
-    </row>
-    <row r="748" ht="15.75" customHeight="1">
-      <c r="A748" s="13"/>
-    </row>
-    <row r="749" ht="15.75" customHeight="1">
-      <c r="A749" s="13"/>
-    </row>
-    <row r="750" ht="15.75" customHeight="1">
-      <c r="A750" s="13"/>
-    </row>
-    <row r="751" ht="15.75" customHeight="1">
-      <c r="A751" s="13"/>
-    </row>
-    <row r="752" ht="15.75" customHeight="1">
-      <c r="A752" s="13"/>
-    </row>
-    <row r="753" ht="15.75" customHeight="1">
-      <c r="A753" s="13"/>
-    </row>
-    <row r="754" ht="15.75" customHeight="1">
-      <c r="A754" s="13"/>
-    </row>
-    <row r="755" ht="15.75" customHeight="1">
-      <c r="A755" s="13"/>
-    </row>
-    <row r="756" ht="15.75" customHeight="1">
-      <c r="A756" s="13"/>
-    </row>
-    <row r="757" ht="15.75" customHeight="1">
-      <c r="A757" s="13"/>
-    </row>
-    <row r="758" ht="15.75" customHeight="1">
-      <c r="A758" s="13"/>
-    </row>
-    <row r="759" ht="15.75" customHeight="1">
-      <c r="A759" s="13"/>
-    </row>
-    <row r="760" ht="15.75" customHeight="1">
-      <c r="A760" s="13"/>
-    </row>
-    <row r="761" ht="15.75" customHeight="1">
-      <c r="A761" s="13"/>
-    </row>
-    <row r="762" ht="15.75" customHeight="1">
-      <c r="A762" s="13"/>
-    </row>
-    <row r="763" ht="15.75" customHeight="1">
-      <c r="A763" s="13"/>
-    </row>
-    <row r="764" ht="15.75" customHeight="1">
-      <c r="A764" s="13"/>
-    </row>
-    <row r="765" ht="15.75" customHeight="1">
-      <c r="A765" s="13"/>
-    </row>
-    <row r="766" ht="15.75" customHeight="1">
-      <c r="A766" s="13"/>
-    </row>
-    <row r="767" ht="15.75" customHeight="1">
-      <c r="A767" s="13"/>
-    </row>
-    <row r="768" ht="15.75" customHeight="1">
-      <c r="A768" s="13"/>
-    </row>
-    <row r="769" ht="15.75" customHeight="1">
-      <c r="A769" s="13"/>
-    </row>
-    <row r="770" ht="15.75" customHeight="1">
-      <c r="A770" s="13"/>
-    </row>
-    <row r="771" ht="15.75" customHeight="1">
-      <c r="A771" s="13"/>
-    </row>
-    <row r="772" ht="15.75" customHeight="1">
-      <c r="A772" s="13"/>
-    </row>
-    <row r="773" ht="15.75" customHeight="1">
-      <c r="A773" s="13"/>
-    </row>
-    <row r="774" ht="15.75" customHeight="1">
-      <c r="A774" s="13"/>
-    </row>
-    <row r="775" ht="15.75" customHeight="1">
-      <c r="A775" s="13"/>
-    </row>
-    <row r="776" ht="15.75" customHeight="1">
-      <c r="A776" s="13"/>
-    </row>
-    <row r="777" ht="15.75" customHeight="1">
-      <c r="A777" s="13"/>
-    </row>
-    <row r="778" ht="15.75" customHeight="1">
-      <c r="A778" s="13"/>
-    </row>
-    <row r="779" ht="15.75" customHeight="1">
-      <c r="A779" s="13"/>
-    </row>
-    <row r="780" ht="15.75" customHeight="1">
-      <c r="A780" s="13"/>
-    </row>
-    <row r="781" ht="15.75" customHeight="1">
-      <c r="A781" s="13"/>
-    </row>
-    <row r="782" ht="15.75" customHeight="1">
-      <c r="A782" s="13"/>
-    </row>
-    <row r="783" ht="15.75" customHeight="1">
-      <c r="A783" s="13"/>
-    </row>
-    <row r="784" ht="15.75" customHeight="1">
-      <c r="A784" s="13"/>
-    </row>
-    <row r="785" ht="15.75" customHeight="1">
-      <c r="A785" s="13"/>
-    </row>
-    <row r="786" ht="15.75" customHeight="1">
-      <c r="A786" s="13"/>
-    </row>
-    <row r="787" ht="15.75" customHeight="1">
-      <c r="A787" s="13"/>
-    </row>
-    <row r="788" ht="15.75" customHeight="1">
-      <c r="A788" s="13"/>
-    </row>
-    <row r="789" ht="15.75" customHeight="1">
-      <c r="A789" s="13"/>
-    </row>
-    <row r="790" ht="15.75" customHeight="1">
-      <c r="A790" s="13"/>
-    </row>
-    <row r="791" ht="15.75" customHeight="1">
-      <c r="A791" s="13"/>
-    </row>
-    <row r="792" ht="15.75" customHeight="1">
-      <c r="A792" s="13"/>
-    </row>
-    <row r="793" ht="15.75" customHeight="1">
-      <c r="A793" s="13"/>
-    </row>
-    <row r="794" ht="15.75" customHeight="1">
-      <c r="A794" s="13"/>
-    </row>
-    <row r="795" ht="15.75" customHeight="1">
-      <c r="A795" s="13"/>
-    </row>
-    <row r="796" ht="15.75" customHeight="1">
-      <c r="A796" s="13"/>
-    </row>
-    <row r="797" ht="15.75" customHeight="1">
-      <c r="A797" s="13"/>
-    </row>
-    <row r="798" ht="15.75" customHeight="1">
-      <c r="A798" s="13"/>
-    </row>
-    <row r="799" ht="15.75" customHeight="1">
-      <c r="A799" s="13"/>
-    </row>
-    <row r="800" ht="15.75" customHeight="1">
-      <c r="A800" s="13"/>
-    </row>
-    <row r="801" ht="15.75" customHeight="1">
-      <c r="A801" s="13"/>
-    </row>
-    <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="13"/>
-    </row>
-    <row r="803" ht="15.75" customHeight="1">
-      <c r="A803" s="13"/>
-    </row>
-    <row r="804" ht="15.75" customHeight="1">
-      <c r="A804" s="13"/>
-    </row>
-    <row r="805" ht="15.75" customHeight="1">
-      <c r="A805" s="13"/>
-    </row>
-    <row r="806" ht="15.75" customHeight="1">
-      <c r="A806" s="13"/>
-    </row>
-    <row r="807" ht="15.75" customHeight="1">
-      <c r="A807" s="13"/>
-    </row>
-    <row r="808" ht="15.75" customHeight="1">
-      <c r="A808" s="13"/>
-    </row>
-    <row r="809" ht="15.75" customHeight="1">
-      <c r="A809" s="13"/>
-    </row>
-    <row r="810" ht="15.75" customHeight="1">
-      <c r="A810" s="13"/>
-    </row>
-    <row r="811" ht="15.75" customHeight="1">
-      <c r="A811" s="13"/>
-    </row>
-    <row r="812" ht="15.75" customHeight="1">
-      <c r="A812" s="13"/>
-    </row>
-    <row r="813" ht="15.75" customHeight="1">
-      <c r="A813" s="13"/>
-    </row>
-    <row r="814" ht="15.75" customHeight="1">
-      <c r="A814" s="13"/>
-    </row>
-    <row r="815" ht="15.75" customHeight="1">
-      <c r="A815" s="13"/>
-    </row>
-    <row r="816" ht="15.75" customHeight="1">
-      <c r="A816" s="13"/>
-    </row>
-    <row r="817" ht="15.75" customHeight="1">
-      <c r="A817" s="13"/>
-    </row>
-    <row r="818" ht="15.75" customHeight="1">
-      <c r="A818" s="13"/>
-    </row>
-    <row r="819" ht="15.75" customHeight="1">
-      <c r="A819" s="13"/>
-    </row>
-    <row r="820" ht="15.75" customHeight="1">
-      <c r="A820" s="13"/>
-    </row>
-    <row r="821" ht="15.75" customHeight="1">
-      <c r="A821" s="13"/>
-    </row>
-    <row r="822" ht="15.75" customHeight="1">
-      <c r="A822" s="13"/>
-    </row>
-    <row r="823" ht="15.75" customHeight="1">
-      <c r="A823" s="13"/>
-    </row>
-    <row r="824" ht="15.75" customHeight="1">
-      <c r="A824" s="13"/>
-    </row>
-    <row r="825" ht="15.75" customHeight="1">
-      <c r="A825" s="13"/>
-    </row>
-    <row r="826" ht="15.75" customHeight="1">
-      <c r="A826" s="13"/>
-    </row>
-    <row r="827" ht="15.75" customHeight="1">
-      <c r="A827" s="13"/>
-    </row>
-    <row r="828" ht="15.75" customHeight="1">
-      <c r="A828" s="13"/>
-    </row>
-    <row r="829" ht="15.75" customHeight="1">
-      <c r="A829" s="13"/>
-    </row>
-    <row r="830" ht="15.75" customHeight="1">
-      <c r="A830" s="13"/>
-    </row>
-    <row r="831" ht="15.75" customHeight="1">
-      <c r="A831" s="13"/>
-    </row>
-    <row r="832" ht="15.75" customHeight="1">
-      <c r="A832" s="13"/>
-    </row>
-    <row r="833" ht="15.75" customHeight="1">
-      <c r="A833" s="13"/>
-    </row>
-    <row r="834" ht="15.75" customHeight="1">
-      <c r="A834" s="13"/>
-    </row>
-    <row r="835" ht="15.75" customHeight="1">
-      <c r="A835" s="13"/>
-    </row>
-    <row r="836" ht="15.75" customHeight="1">
-      <c r="A836" s="13"/>
-    </row>
-    <row r="837" ht="15.75" customHeight="1">
-      <c r="A837" s="13"/>
-    </row>
-    <row r="838" ht="15.75" customHeight="1">
-      <c r="A838" s="13"/>
-    </row>
-    <row r="839" ht="15.75" customHeight="1">
-      <c r="A839" s="13"/>
-    </row>
-    <row r="840" ht="15.75" customHeight="1">
-      <c r="A840" s="13"/>
-    </row>
-    <row r="841" ht="15.75" customHeight="1">
-      <c r="A841" s="13"/>
-    </row>
-    <row r="842" ht="15.75" customHeight="1">
-      <c r="A842" s="13"/>
-    </row>
-    <row r="843" ht="15.75" customHeight="1">
-      <c r="A843" s="13"/>
-    </row>
-    <row r="844" ht="15.75" customHeight="1">
-      <c r="A844" s="13"/>
-    </row>
-    <row r="845" ht="15.75" customHeight="1">
-      <c r="A845" s="13"/>
-    </row>
-    <row r="846" ht="15.75" customHeight="1">
-      <c r="A846" s="13"/>
-    </row>
-    <row r="847" ht="15.75" customHeight="1">
-      <c r="A847" s="13"/>
-    </row>
-    <row r="848" ht="15.75" customHeight="1">
-      <c r="A848" s="13"/>
-    </row>
-    <row r="849" ht="15.75" customHeight="1">
-      <c r="A849" s="13"/>
-    </row>
-    <row r="850" ht="15.75" customHeight="1">
-      <c r="A850" s="13"/>
-    </row>
-    <row r="851" ht="15.75" customHeight="1">
-      <c r="A851" s="13"/>
-    </row>
-    <row r="852" ht="15.75" customHeight="1">
-      <c r="A852" s="13"/>
-    </row>
-    <row r="853" ht="15.75" customHeight="1">
-      <c r="A853" s="13"/>
-    </row>
-    <row r="854" ht="15.75" customHeight="1">
-      <c r="A854" s="13"/>
-    </row>
-    <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="13"/>
-    </row>
-    <row r="856" ht="15.75" customHeight="1">
-      <c r="A856" s="13"/>
-    </row>
-    <row r="857" ht="15.75" customHeight="1">
-      <c r="A857" s="13"/>
-    </row>
-    <row r="858" ht="15.75" customHeight="1">
-      <c r="A858" s="13"/>
-    </row>
-    <row r="859" ht="15.75" customHeight="1">
-      <c r="A859" s="13"/>
-    </row>
-    <row r="860" ht="15.75" customHeight="1">
-      <c r="A860" s="13"/>
-    </row>
-    <row r="861" ht="15.75" customHeight="1">
-      <c r="A861" s="13"/>
-    </row>
-    <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="13"/>
-    </row>
-    <row r="863" ht="15.75" customHeight="1">
-      <c r="A863" s="13"/>
-    </row>
-    <row r="864" ht="15.75" customHeight="1">
-      <c r="A864" s="13"/>
-    </row>
-    <row r="865" ht="15.75" customHeight="1">
-      <c r="A865" s="13"/>
-    </row>
-    <row r="866" ht="15.75" customHeight="1">
-      <c r="A866" s="13"/>
-    </row>
-    <row r="867" ht="15.75" customHeight="1">
-      <c r="A867" s="13"/>
-    </row>
-    <row r="868" ht="15.75" customHeight="1">
-      <c r="A868" s="13"/>
-    </row>
-    <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="13"/>
-    </row>
-    <row r="870" ht="15.75" customHeight="1">
-      <c r="A870" s="13"/>
-    </row>
-    <row r="871" ht="15.75" customHeight="1">
-      <c r="A871" s="13"/>
-    </row>
-    <row r="872" ht="15.75" customHeight="1">
-      <c r="A872" s="13"/>
-    </row>
-    <row r="873" ht="15.75" customHeight="1">
-      <c r="A873" s="13"/>
-    </row>
-    <row r="874" ht="15.75" customHeight="1">
-      <c r="A874" s="13"/>
-    </row>
-    <row r="875" ht="15.75" customHeight="1">
-      <c r="A875" s="13"/>
-    </row>
-    <row r="876" ht="15.75" customHeight="1">
-      <c r="A876" s="13"/>
-    </row>
-    <row r="877" ht="15.75" customHeight="1">
-      <c r="A877" s="13"/>
-    </row>
-    <row r="878" ht="15.75" customHeight="1">
-      <c r="A878" s="13"/>
-    </row>
-    <row r="879" ht="15.75" customHeight="1">
-      <c r="A879" s="13"/>
-    </row>
-    <row r="880" ht="15.75" customHeight="1">
-      <c r="A880" s="13"/>
-    </row>
-    <row r="881" ht="15.75" customHeight="1">
-      <c r="A881" s="13"/>
-    </row>
-    <row r="882" ht="15.75" customHeight="1">
-      <c r="A882" s="13"/>
-    </row>
-    <row r="883" ht="15.75" customHeight="1">
-      <c r="A883" s="13"/>
-    </row>
-    <row r="884" ht="15.75" customHeight="1">
-      <c r="A884" s="13"/>
-    </row>
-    <row r="885" ht="15.75" customHeight="1">
-      <c r="A885" s="13"/>
-    </row>
-    <row r="886" ht="15.75" customHeight="1">
-      <c r="A886" s="13"/>
-    </row>
-    <row r="887" ht="15.75" customHeight="1">
-      <c r="A887" s="13"/>
-    </row>
-    <row r="888" ht="15.75" customHeight="1">
-      <c r="A888" s="13"/>
-    </row>
-    <row r="889" ht="15.75" customHeight="1">
-      <c r="A889" s="13"/>
-    </row>
-    <row r="890" ht="15.75" customHeight="1">
-      <c r="A890" s="13"/>
-    </row>
-    <row r="891" ht="15.75" customHeight="1">
-      <c r="A891" s="13"/>
-    </row>
-    <row r="892" ht="15.75" customHeight="1">
-      <c r="A892" s="13"/>
-    </row>
-    <row r="893" ht="15.75" customHeight="1">
-      <c r="A893" s="13"/>
-    </row>
-    <row r="894" ht="15.75" customHeight="1">
-      <c r="A894" s="13"/>
-    </row>
-    <row r="895" ht="15.75" customHeight="1">
-      <c r="A895" s="13"/>
-    </row>
-    <row r="896" ht="15.75" customHeight="1">
-      <c r="A896" s="13"/>
-    </row>
-    <row r="897" ht="15.75" customHeight="1">
-      <c r="A897" s="13"/>
-    </row>
-    <row r="898" ht="15.75" customHeight="1">
-      <c r="A898" s="13"/>
-    </row>
-    <row r="899" ht="15.75" customHeight="1">
-      <c r="A899" s="13"/>
-    </row>
-    <row r="900" ht="15.75" customHeight="1">
-      <c r="A900" s="13"/>
-    </row>
-    <row r="901" ht="15.75" customHeight="1">
-      <c r="A901" s="13"/>
-    </row>
-    <row r="902" ht="15.75" customHeight="1">
-      <c r="A902" s="13"/>
-    </row>
-    <row r="903" ht="15.75" customHeight="1">
-      <c r="A903" s="13"/>
-    </row>
-    <row r="904" ht="15.75" customHeight="1">
-      <c r="A904" s="13"/>
-    </row>
-    <row r="905" ht="15.75" customHeight="1">
-      <c r="A905" s="13"/>
-    </row>
-    <row r="906" ht="15.75" customHeight="1">
-      <c r="A906" s="13"/>
-    </row>
-    <row r="907" ht="15.75" customHeight="1">
-      <c r="A907" s="13"/>
-    </row>
-    <row r="908" ht="15.75" customHeight="1">
-      <c r="A908" s="13"/>
-    </row>
-    <row r="909" ht="15.75" customHeight="1">
-      <c r="A909" s="13"/>
-    </row>
-    <row r="910" ht="15.75" customHeight="1">
-      <c r="A910" s="13"/>
-    </row>
-    <row r="911" ht="15.75" customHeight="1">
-      <c r="A911" s="13"/>
-    </row>
-    <row r="912" ht="15.75" customHeight="1">
-      <c r="A912" s="13"/>
-    </row>
-    <row r="913" ht="15.75" customHeight="1">
-      <c r="A913" s="13"/>
-    </row>
-    <row r="914" ht="15.75" customHeight="1">
-      <c r="A914" s="13"/>
-    </row>
-    <row r="915" ht="15.75" customHeight="1">
-      <c r="A915" s="13"/>
-    </row>
-    <row r="916" ht="15.75" customHeight="1">
-      <c r="A916" s="13"/>
-    </row>
-    <row r="917" ht="15.75" customHeight="1">
-      <c r="A917" s="13"/>
-    </row>
-    <row r="918" ht="15.75" customHeight="1">
-      <c r="A918" s="13"/>
-    </row>
-    <row r="919" ht="15.75" customHeight="1">
-      <c r="A919" s="13"/>
-    </row>
-    <row r="920" ht="15.75" customHeight="1">
-      <c r="A920" s="13"/>
-    </row>
-    <row r="921" ht="15.75" customHeight="1">
-      <c r="A921" s="13"/>
-    </row>
-    <row r="922" ht="15.75" customHeight="1">
-      <c r="A922" s="13"/>
-    </row>
-    <row r="923" ht="15.75" customHeight="1">
-      <c r="A923" s="13"/>
-    </row>
-    <row r="924" ht="15.75" customHeight="1">
-      <c r="A924" s="13"/>
-    </row>
-    <row r="925" ht="15.75" customHeight="1">
-      <c r="A925" s="13"/>
-    </row>
-    <row r="926" ht="15.75" customHeight="1">
-      <c r="A926" s="13"/>
-    </row>
-    <row r="927" ht="15.75" customHeight="1">
-      <c r="A927" s="13"/>
-    </row>
-    <row r="928" ht="15.75" customHeight="1">
-      <c r="A928" s="13"/>
-    </row>
-    <row r="929" ht="15.75" customHeight="1">
-      <c r="A929" s="13"/>
-    </row>
-    <row r="930" ht="15.75" customHeight="1">
-      <c r="A930" s="13"/>
-    </row>
-    <row r="931" ht="15.75" customHeight="1">
-      <c r="A931" s="13"/>
-    </row>
-    <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="13"/>
-    </row>
-    <row r="933" ht="15.75" customHeight="1">
-      <c r="A933" s="13"/>
-    </row>
-    <row r="934" ht="15.75" customHeight="1">
-      <c r="A934" s="13"/>
-    </row>
-    <row r="935" ht="15.75" customHeight="1">
-      <c r="A935" s="13"/>
-    </row>
-    <row r="936" ht="15.75" customHeight="1">
-      <c r="A936" s="13"/>
-    </row>
-    <row r="937" ht="15.75" customHeight="1">
-      <c r="A937" s="13"/>
-    </row>
-    <row r="938" ht="15.75" customHeight="1">
-      <c r="A938" s="13"/>
-    </row>
-    <row r="939" ht="15.75" customHeight="1">
-      <c r="A939" s="13"/>
-    </row>
-    <row r="940" ht="15.75" customHeight="1">
-      <c r="A940" s="13"/>
-    </row>
-    <row r="941" ht="15.75" customHeight="1">
-      <c r="A941" s="13"/>
-    </row>
-    <row r="942" ht="15.75" customHeight="1">
-      <c r="A942" s="13"/>
-    </row>
-    <row r="943" ht="15.75" customHeight="1">
-      <c r="A943" s="13"/>
-    </row>
-    <row r="944" ht="15.75" customHeight="1">
-      <c r="A944" s="13"/>
-    </row>
-    <row r="945" ht="15.75" customHeight="1">
-      <c r="A945" s="13"/>
-    </row>
-    <row r="946" ht="15.75" customHeight="1">
-      <c r="A946" s="13"/>
-    </row>
-    <row r="947" ht="15.75" customHeight="1">
-      <c r="A947" s="13"/>
-    </row>
-    <row r="948" ht="15.75" customHeight="1">
-      <c r="A948" s="13"/>
-    </row>
-    <row r="949" ht="15.75" customHeight="1">
-      <c r="A949" s="13"/>
-    </row>
-    <row r="950" ht="15.75" customHeight="1">
-      <c r="A950" s="13"/>
-    </row>
-    <row r="951" ht="15.75" customHeight="1">
-      <c r="A951" s="13"/>
-    </row>
-    <row r="952" ht="15.75" customHeight="1">
-      <c r="A952" s="13"/>
-    </row>
-    <row r="953" ht="15.75" customHeight="1">
-      <c r="A953" s="13"/>
-    </row>
-    <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="13"/>
-    </row>
-    <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="13"/>
-    </row>
-    <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="13"/>
-    </row>
-    <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="13"/>
-    </row>
-    <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="13"/>
-    </row>
-    <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="13"/>
-    </row>
-    <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="13"/>
-    </row>
-    <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="13"/>
-    </row>
-    <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="13"/>
-    </row>
-    <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="13"/>
-    </row>
-    <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="13"/>
-    </row>
-    <row r="965" ht="15.75" customHeight="1">
-      <c r="A965" s="13"/>
-    </row>
-    <row r="966" ht="15.75" customHeight="1">
-      <c r="A966" s="13"/>
-    </row>
-    <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="13"/>
-    </row>
-    <row r="968" ht="15.75" customHeight="1">
-      <c r="A968" s="13"/>
-    </row>
-    <row r="969" ht="15.75" customHeight="1">
-      <c r="A969" s="13"/>
-    </row>
-    <row r="970" ht="15.75" customHeight="1">
-      <c r="A970" s="13"/>
-    </row>
-    <row r="971" ht="15.75" customHeight="1">
-      <c r="A971" s="13"/>
-    </row>
-    <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="13"/>
-    </row>
-    <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="13"/>
-    </row>
-    <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="13"/>
-    </row>
-    <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="13"/>
-    </row>
-    <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="13"/>
-    </row>
-    <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="13"/>
-    </row>
-    <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="13"/>
-    </row>
-    <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="13"/>
-    </row>
-    <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="13"/>
-    </row>
-    <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="13"/>
-    </row>
-    <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="13"/>
-    </row>
-    <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="13"/>
-    </row>
-    <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="13"/>
-    </row>
-    <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="13"/>
-    </row>
-    <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="13"/>
-    </row>
-    <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="13"/>
-    </row>
-    <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="13"/>
-    </row>
-    <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="13"/>
-    </row>
-    <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="13"/>
-    </row>
-    <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="13"/>
-    </row>
-    <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="13"/>
-    </row>
-    <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="13"/>
-    </row>
-    <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="13"/>
-    </row>
-    <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="13"/>
-    </row>
-    <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="13"/>
-    </row>
-    <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="13"/>
-    </row>
-    <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="13"/>
-    </row>
-    <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="13"/>
-    </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="13"/>
-    </row>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
